--- a/important_mails_2026-05-20.xlsx
+++ b/important_mails_2026-05-20.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -537,12 +537,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -552,21 +552,167 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 14:33:15 +0000</t>
+          <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Balance paid on your Amazon seller account</t>
+          <t>Your payment is on the way</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 05/20/26 13:53 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 240.42.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 15:00:47 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Votre paiement est en cours</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Félicitations ! Votre paiement est en cours et arrivera sous peu.
+ Tentative de versement
+Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
+Le 05/20/26 15:00 CEST, nous avons effectué un virement d’un montant de €
+ 176.44 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
+ Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
+ Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
+ Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de p</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 13:54:37 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento elaborato con successo</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
+ Tentativo di pagamento
+Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
+In data 05/20/26 13:54 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
+ 223,62.
+ Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
+ Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
+ Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 17 May 2026 14:33:15 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Balance paid on your Amazon seller account</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
@@ -582,39 +728,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -640,39 +786,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -689,39 +835,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -738,39 +884,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -790,39 +936,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -846,39 +992,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -902,39 +1048,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -954,39 +1100,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1006,39 +1152,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1058,39 +1204,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1110,39 +1256,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -1158,39 +1304,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1207,39 +1353,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1259,88 +1405,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 13 May 2026 14:53:51 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Download your China tax report for October - December 2025</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96
- You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
- Hello,
-According to rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
-We’ve submitted your quarterly tax report covering October to December 2025, which includes your identity information, number of transactions, revenue, and commission and service fees.
-We’re re-sending your quarterly China tax report in case you didn’t download it in April 2026. The links below are active for seven days.
- Download your quarterly report
-This report is provided for your reference only, no action is required.
-Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
- Download your order-level report
- Note : Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
-We’ll continue to provide you with q</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1359,40 +1456,40 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1408,40 +1505,40 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1455,40 +1552,40 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -1502,40 +1599,40 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -1548,39 +1645,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -1600,39 +1697,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -1657,39 +1754,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -1714,39 +1811,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:10:53 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -1764,39 +1861,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:55:42 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Ship Smarter: Get 3 FREE Brokerage Fees: Limited Time C2S2 Offer 🚀</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z3hy11/6664114770/h/cIM7P1R6ABFsNRmzeIU2ASpTCxzOevVrUjDi2lts12A)
 Ship Cross-Border &amp; Save Big. Get Started with C2S2 Today.
@@ -1813,39 +1910,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 06:33:16 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1864,39 +1961,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:48:46 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1911,40 +2008,40 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 05:21:00 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1960,39 +2057,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 17:10:29 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -2008,39 +2105,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:52:25 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;store-news@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>EchoPlan Magnetic Blocks is still in your cart</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Still thinking about it? https://www.amazon.com/gp/cart/view.html?ref_=cor
 EchoPlan 200PCS Magnetic Blocks, Magnetic Building Blocks, Magnet Blocks Cubes, STEM Educational Stacking Magnet Toy for Kids Ages 3 4 5 6 7 8 9 10 11, Birthday Gifts for Boys and Girls, 1&amp;quot; Large Size
@@ -2061,39 +2158,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:07:42 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2108,39 +2205,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 03:00:00 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -2170,39 +2267,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 16:40:18 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -2230,87 +2327,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 13 May 2026 14:51:48 +0000</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
- Dzień dobry,
-zgodnie z zasadami dotyczącymi sklepów internetowych wydanymi przez Radę Państwa Chin (dekret nr 810) jesteśmy zobowiązani do przekazywania informacji o sprzedawcach z siedzibą w Chinach tamtejszemu organowi podatkowemu w cyklach kwartalnych.
-Przesłaliśmy Twój kwartalny raport podatkowy za okres od października do grudnia 2025 r., który zawiera Twoje dane identyfikacyjne, liczbę transakcji, przychody oraz prowizje i opłaty za usługi.
-Ponownie wysyłamy Twój kwartalny raport podatkowy dla Chin na wypadek, gdyby nie został on pobrany w kwietniu 2026 r. Poniższe linki są aktywne przez siedem dni.
- Pobierz raport kwartalny
-Raport ten jest przeznaczony wyłącznie do wglądu. Nie jest wymagane żadne działanie.
-Na podstawie opinii udostępniliśmy również bardziej szczegółowy raport na poziomie zamówienia, który przedstawia informacje kwartalne z podziałem na transakcje.
- Pobierz raport z informacjami na poziomie zamówienia
- Uwaga: Mogą wystąpić różnice między danymi w tych raportach a raportem o płatnościach </t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2334,39 +2383,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2387,39 +2436,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2442,39 +2491,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2490,39 +2539,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2547,39 +2596,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2599,39 +2648,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2651,39 +2700,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2703,39 +2752,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2756,39 +2805,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2808,39 +2857,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2860,39 +2909,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -2908,39 +2957,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2960,39 +3009,88 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 14:53:51 +0000</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Download your China tax report for October - December 2025</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>96
+ You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
+ Hello,
+According to rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
+We’ve submitted your quarterly tax report covering October to December 2025, which includes your identity information, number of transactions, revenue, and commission and service fees.
+We’re re-sending your quarterly China tax report in case you didn’t download it in April 2026. The links below are active for seven days.
+ Download your quarterly report
+This report is provided for your reference only, no action is required.
+Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
+ Download your order-level report
+ Note : Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
+We’ll continue to provide you with q</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3009,39 +3107,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3061,39 +3159,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3113,39 +3211,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3162,39 +3260,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -3209,39 +3307,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3257,39 +3355,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3309,39 +3407,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3361,39 +3459,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3410,39 +3508,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3462,39 +3560,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3514,39 +3612,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3563,39 +3661,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3615,39 +3713,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3661,39 +3759,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3713,39 +3811,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3762,40 +3860,40 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3810,40 +3908,40 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3857,40 +3955,40 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3904,41 +4002,41 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -3949,39 +4047,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4000,39 +4098,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4056,39 +4154,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4106,39 +4204,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4156,39 +4254,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4206,39 +4304,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4256,39 +4354,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4306,39 +4404,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4354,39 +4452,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4404,39 +4502,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4454,39 +4552,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4496,39 +4594,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -4549,39 +4647,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4597,39 +4695,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4648,39 +4746,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -4691,39 +4789,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4742,39 +4840,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4793,39 +4891,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4844,39 +4942,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4896,39 +4994,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -4957,39 +5055,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -5007,39 +5105,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5057,39 +5155,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5107,39 +5205,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -5153,39 +5251,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5203,110 +5301,10 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
- A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-● The document uploaded for "B0DD7R3PPG" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was created
-Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
-For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
-Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these product/other products, please submit them ( for each ASIN separately ) in "Account Health Dashboard" under the relevant Appeal reason:
-1. Go to the Account Health page and select the Regulatory Compliance tab
-2. Choose next steps.
-3. Click Submit button for the product y</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
- DOC REVIEW</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-● The document uploaded for "B0FCDRNTT8x`" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was created
-Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
-For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
-Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these product/other products, please submit them ( for each ASIN separately ) in "Account Health Dashboard" under the relevant Appeal reason:
-1. Go to the Account Health page and select the Regulatory Compliance tab
-2. Choose next steps.
-3. Click Submit button for the product</t>
-        </is>
-      </c>
-    </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5321,51 +5319,33 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
+          <t>Wed, 13 May 2026 14:51:48 +0000</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
+          <t>Zespół Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Amazon DV TIC</t>
+          <t>Pobierz raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>尊敬的卖家，您好。
-我们可以为您提供亚马逊DV验证报告服务。
-验证费用：
-【玩具】500元（RMB）/ASIN；
-【电动自行车用充电器及电池】4500元（RMB）/ASIN；
-【移动电源及便携式电源产品】5000元（RMB）/ASIN。
-如涉及较多ASIN或有其他需求，我们将根据具体情况提供优惠报价。
-商品测试：
-如您的商品需额外进行合规测试，请提供实物图片和商品参数以及销售国家等，以便评估测试费用。
-服务流程如下：
-登录卖家中心 “合规管理”（MYC）；
-针对待处理 ASIN，选择 “CVC威凯” 提交验证申请；
-提供所需资料：申请表、测试报告、产品六面实物照片（非包装图）、标签警示语、用户手册/使用说明书等；
-CVC威凯将进行检测或合规验证，并将结果直接提交亚马逊；如需整改，我们会及时与您沟通。
-如需进一步了解或希望直接安排服务，可直接通过以下方式联系我，我们将全程协助您完成验证流程。
-您也可联系官方邮箱专员咨询：amazondv@cei1958.com
-感谢您的支持，期待与您合作！
-如您已经对接我司业务员，请忽略此信息，不便之处敬请谅解。
-Dear Seller,
-Greetings.
-We are pleased to offer Amazon DV Verification Report services to support your compliance needs.
-Verification Fee:
-【Toys】¥500 (RMB) per ASIN.
-【E-bikes lithium-ion batteries and chargers】¥4500 (RMB) per ASIN.
-【Power Bank and Portable Power Station】¥5000 (RMB) per ASIN.
-If you have multiple ASINs or special requirements, we can provide a customized discounted quote based on your situation.
-Product Testing:If your product requires additional compliance testing, please provide physical product photos, specify the target sales country/region and product parameter so we can assess the testing fees accordingly.
-Service Process:
-Log in to your Seller Central and navigate to “Compliance Managemen</t>
+          <t xml:space="preserve">96
+ Możesz teraz pobrać kwartalny raport podatkowy, który zawiera dane, takie jak informacje identyfikacyjne, liczba transakcji, przychody oraz prowizje i opłaty za usługi.
+ Dzień dobry,
+zgodnie z zasadami dotyczącymi sklepów internetowych wydanymi przez Radę Państwa Chin (dekret nr 810) jesteśmy zobowiązani do przekazywania informacji o sprzedawcach z siedzibą w Chinach tamtejszemu organowi podatkowemu w cyklach kwartalnych.
+Przesłaliśmy Twój kwartalny raport podatkowy za okres od października do grudnia 2025 r., który zawiera Twoje dane identyfikacyjne, liczbę transakcji, przychody oraz prowizje i opłaty za usługi.
+Ponownie wysyłamy Twój kwartalny raport podatkowy dla Chin na wypadek, gdyby nie został on pobrany w kwietniu 2026 r. Poniższe linki są aktywne przez siedem dni.
+ Pobierz raport kwartalny
+Raport ten jest przeznaczony wyłącznie do wglądu. Nie jest wymagane żadne działanie.
+Na podstawie opinii udostępniliśmy również bardziej szczegółowy raport na poziomie zamówienia, który przedstawia informacje kwartalne z podziałem na transakcje.
+ Pobierz raport z informacjami na poziomie zamówienia
+ Uwaga: Mogą wystąpić różnice między danymi w tych raportach a raportem o płatnościach </t>
         </is>
       </c>
     </row>
@@ -9426,7 +9406,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -9441,74 +9421,21 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
+          <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Dein Einkaufswagen wartet</t>
+          <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
- 21,81 €
-https://www.amazon.de/gp/product/B0DRCF83VZ/?ref_=
-Einkaufswagen anzeigen
-https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schaue dir weitere Optionen an
-Roaxkois Keramik Bemalen Set - Kreatives Keramik Bastelset mit Farben, Pinseln und Anleitungen, Perfektes Tassen Bemalen Set für individuelle Geschenke und Freizeitgestaltung
- 20,97 €
-https://www.amazon.de/gp/product/B0FD8PWPNK/?ref_=ci_mcx_mr_2p_0_lm
-Roaxkois Keramik Bemalen Set - Kreatives Keramik Bastelset mit Farben, Pinseln und Anleitungen, Perfektes Tassen Bemalen Set für individuelle Geschenke und Freizeitgestaltung (Glatt) (Glatt)
- -17 % 20,97 € UVP: 25,17 €
-https://www.amazon.de/gp/product/B0G6ZCHV7Z/?ref_=ci_mcx_mr_2p_1_lm
-LEOSINYIN Keramik Bemalen Set, Tassen Bemalen Set, DIY Keramik Malset Kreatives Geschenk für Kinder &amp;amp; Erwachsene Enthält 2*Tassen, 2*Farbwanne, 4*Pinsel, 2 * 12 Farben und Anleitung
-Befristetes Angebot -40 % 17,99 € UVP: 29,99 €
-https://www.amazon.de/gp/prod</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 9 May 2026 04:43:42 +0000</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-05-21</t>
-        </is>
-      </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9532,39 +9459,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9587,39 +9514,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9643,39 +9570,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9699,39 +9626,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9752,39 +9679,39 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
@@ -9793,39 +9720,39 @@
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9855,39 +9782,39 @@
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F189" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除

--- a/important_mails_2026-05-20.xlsx
+++ b/important_mails_2026-05-20.xlsx
@@ -2270,7 +2270,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2285,81 +2285,21 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Wed, 13 May 2026 16:40:18 +0000</t>
+          <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Worten Marketplace - Portugal y España</t>
+          <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Hola Weihai EU,
-Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
-Nuestro equipo de
-análisis ha señalado que una asociación con usted sería una gran oportunidad
-para ambos.
-¿Estaría
-disponible para una reunión online esta semana?
-Acerca de Worten
-- Somos el líder del mercado portugués:
-- Nº 1 del
-comercio electrónico portugués
-- Sitio web con
-mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
-- Más de 200
-tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
-- Plataforma de
-gestión: Mirakl (se puede integrar manualmente o vía API)
-- Sin costes los 6 meses iniciales
-Estaré encantado
-de ayudarle si tiene alguna pregunta.
-Muchas gracias,
-Saludos
-Cordiales</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 16 May 2026 04:51:55 +0000</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-05-28</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2383,39 +2323,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2436,39 +2376,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2491,39 +2431,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2539,39 +2479,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2596,39 +2536,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2648,39 +2588,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2700,39 +2640,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2752,39 +2692,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2805,39 +2745,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 13:03:07 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (2604121A02)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2857,39 +2797,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 4 May 2026 16:59:42 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (AOOD6vlnxr)</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2909,39 +2849,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $69.79 in an attempt to settle your Amazon seller account balance.
@@ -2957,39 +2897,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 07:28:26 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (5NT+O11io4)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3009,39 +2949,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -3058,39 +2998,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3107,39 +3047,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3159,39 +3099,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3211,39 +3151,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 03:44:19 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3260,39 +3200,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 15:00:39 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 87.72 in an attempt to settle your account balance.
@@ -3307,39 +3247,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 14:45:41 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3355,39 +3295,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:23:38 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3407,39 +3347,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3459,39 +3399,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:27:01 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3508,39 +3448,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:26:48 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3560,39 +3500,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3612,39 +3552,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3661,39 +3601,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3713,39 +3653,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -3759,39 +3699,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3811,39 +3751,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3860,40 +3800,40 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3908,40 +3848,40 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3955,40 +3895,40 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4002,41 +3942,41 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -4047,39 +3987,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 17:50:39 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4098,39 +4038,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 12:49:24 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4154,39 +4094,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 5 May 2026 02:13:07 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4204,39 +4144,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 13:18:47 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4254,39 +4194,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 13:15:01 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4304,39 +4244,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:13:49 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4354,39 +4294,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:19:29 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4404,39 +4344,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 12:52:07 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4452,39 +4392,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:11:27 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4502,39 +4442,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4552,39 +4492,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -4594,39 +4534,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
 卖家您好，
@@ -4647,39 +4587,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4695,39 +4635,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -4746,39 +4686,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -4789,39 +4729,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4840,39 +4780,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4891,39 +4831,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -4942,39 +4882,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4994,39 +4934,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -5055,39 +4995,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -5105,39 +5045,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5155,39 +5095,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5205,39 +5145,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -5251,39 +5191,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5298,6 +5238,66 @@
  If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
 -
  If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 13 May 2026 16:40:18 +0000</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Hola Weihai EU,
+Soy Luana Camargo, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
+Nuestro equipo de
+análisis ha señalado que una asociación con usted sería una gran oportunidad
+para ambos.
+¿Estaría
+disponible para una reunión online esta semana?
+Acerca de Worten
+- Somos el líder del mercado portugués:
+- Nº 1 del
+comercio electrónico portugués
+- Sitio web con
+mayor tráfico de Portugal (más de 10 millones de visitas al mes) - Ranking de mercado
+- Más de 200
+tiendas físicas en Portugal y España, proporcionando una oportunidad omnicanal
+- Plataforma de
+gestión: Mirakl (se puede integrar manualmente o vía API)
+- Sin costes los 6 meses iniciales
+Estaré encantado
+de ayudarle si tiene alguna pregunta.
+Muchas gracias,
+Saludos
+Cordiales</t>
         </is>
       </c>
     </row>
